--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C85A70B6-A1CB-4E9E-915B-D536ABB327C8}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEEADCC-8CB0-4AC1-8457-FD01226FF506}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>OFERTA TOTAL (Bls)</t>
   </si>
@@ -57,9 +68,6 @@
     <t>DON MARIO 2200</t>
   </si>
   <si>
-    <t xml:space="preserve"> -   </t>
-  </si>
-  <si>
     <t>DM 25E23 SE</t>
   </si>
   <si>
@@ -106,9 +114,6 @@
   </si>
   <si>
     <t>37x26 E STS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-   </t>
   </si>
   <si>
     <t>NS 3925 E</t>
@@ -124,6 +129,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -289,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -308,20 +316,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -330,7 +326,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -665,14 +667,14 @@
       <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8">
-        <v>3461</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10">
-        <v>3461</v>
+      <c r="D3" s="12">
+        <v>4026.1374999999998</v>
+      </c>
+      <c r="E3" s="13">
+        <v>3120</v>
+      </c>
+      <c r="F3" s="13">
+        <v>906.13749999999982</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -680,19 +682,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="8">
-        <v>16561</v>
+      <c r="D4" s="12">
+        <v>17866.899999999987</v>
       </c>
       <c r="E4" s="12">
-        <v>900</v>
-      </c>
-      <c r="F4" s="8">
-        <v>15661</v>
+        <v>13145</v>
+      </c>
+      <c r="F4" s="12">
+        <v>4721.8999999999869</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -700,39 +702,39 @@
         <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="12">
+        <v>8038.45</v>
+      </c>
+      <c r="E5" s="13">
+        <v>4170</v>
+      </c>
+      <c r="F5" s="13">
+        <v>3868.45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8">
-        <v>8038</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="10">
-        <v>8038</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="8">
-        <v>9078</v>
+      <c r="D6" s="12">
+        <v>9078.2124999999978</v>
       </c>
       <c r="E6" s="12">
-        <v>140</v>
-      </c>
-      <c r="F6" s="8">
-        <v>8938</v>
+        <v>285</v>
+      </c>
+      <c r="F6" s="12">
+        <v>8793.2124999999978</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -740,39 +742,39 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="12">
+        <v>30986.749999999982</v>
+      </c>
+      <c r="E7" s="13">
+        <v>8336</v>
+      </c>
+      <c r="F7" s="13">
+        <v>22650.749999999982</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="8">
-        <v>33277</v>
-      </c>
-      <c r="E7" s="10">
-        <v>5760</v>
-      </c>
-      <c r="F7" s="10">
-        <v>27517</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="8">
-        <v>5353</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="8">
-        <v>5353</v>
+      <c r="D8" s="12">
+        <v>5353.0874999999996</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>5353.0874999999996</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -780,95 +782,95 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="12">
+        <v>43415.662500000006</v>
+      </c>
+      <c r="E9" s="13">
+        <v>4672</v>
+      </c>
+      <c r="F9" s="13">
+        <v>38743.662500000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8">
-        <v>42253</v>
-      </c>
-      <c r="E9" s="10">
-        <v>3960</v>
-      </c>
-      <c r="F9" s="10">
-        <v>38293</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="12">
+        <v>8945.9374999999982</v>
+      </c>
+      <c r="E10" s="12">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="12">
+        <v>5945.9374999999982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="12">
-        <v>799</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="12">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="C11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="12">
+        <v>1872.075</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1872.075</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="D12" s="12">
+        <v>1914.65</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>1914.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="16">
-        <v>118820</v>
-      </c>
-      <c r="E13" s="16">
-        <v>10760</v>
-      </c>
-      <c r="F13" s="16">
-        <v>108060</v>
+      <c r="D13" s="14">
+        <v>131497.86249999996</v>
+      </c>
+      <c r="E13" s="14">
+        <v>36728</v>
+      </c>
+      <c r="F13" s="14">
+        <v>94769.862499999974</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEEADCC-8CB0-4AC1-8457-FD01226FF506}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13D460CD-3DD4-4C25-9769-1A1252159461}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,10 +671,10 @@
         <v>4026.1374999999998</v>
       </c>
       <c r="E3" s="13">
-        <v>3120</v>
+        <v>3160</v>
       </c>
       <c r="F3" s="13">
-        <v>906.13749999999982</v>
+        <v>866.13749999999982</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>17866.899999999987</v>
+        <v>18045.849999999999</v>
       </c>
       <c r="E4" s="12">
         <v>13145</v>
       </c>
       <c r="F4" s="12">
-        <v>4721.8999999999869</v>
+        <v>4900.8499999999985</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>30986.749999999982</v>
+        <v>33436.499999999985</v>
       </c>
       <c r="E7" s="13">
-        <v>8336</v>
+        <v>8436</v>
       </c>
       <c r="F7" s="13">
-        <v>22650.749999999982</v>
+        <v>25000.499999999985</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>43415.662500000006</v>
+        <v>43380.86250000001</v>
       </c>
       <c r="E9" s="13">
         <v>4672</v>
       </c>
       <c r="F9" s="13">
-        <v>38743.662500000006</v>
+        <v>38708.86250000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>131497.86249999996</v>
+        <v>134091.76249999998</v>
       </c>
       <c r="E13" s="14">
-        <v>36728</v>
+        <v>36868</v>
       </c>
       <c r="F13" s="14">
-        <v>94769.862499999974</v>
+        <v>97223.762499999983</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13D460CD-3DD4-4C25-9769-1A1252159461}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6349DCEC-4B24-4067-9518-497A5377CD2D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>18045.849999999999</v>
+        <v>18045.825000000001</v>
       </c>
       <c r="E4" s="12">
         <v>13145</v>
       </c>
       <c r="F4" s="12">
-        <v>4900.8499999999985</v>
+        <v>4900.8250000000007</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>33436.499999999985</v>
+        <v>33211.424999999981</v>
       </c>
       <c r="E7" s="13">
         <v>8436</v>
       </c>
       <c r="F7" s="13">
-        <v>25000.499999999985</v>
+        <v>24775.424999999981</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>134091.76249999998</v>
+        <v>133866.66250000001</v>
       </c>
       <c r="E13" s="14">
         <v>36868</v>
       </c>
       <c r="F13" s="14">
-        <v>97223.762499999983</v>
+        <v>96998.662499999991</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6349DCEC-4B24-4067-9518-497A5377CD2D}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A14B80-9FC6-4E68-8BEB-B67EB47D15B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="12">
-        <v>8945.9374999999982</v>
+        <v>8743.7250000000004</v>
       </c>
       <c r="E10" s="12">
         <v>3000</v>
       </c>
       <c r="F10" s="12">
-        <v>5945.9374999999982</v>
+        <v>5743.7250000000004</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133866.66250000001</v>
+        <v>133664.45000000001</v>
       </c>
       <c r="E13" s="14">
         <v>36868</v>
       </c>
       <c r="F13" s="14">
-        <v>96998.662499999991</v>
+        <v>96796.45</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A14B80-9FC6-4E68-8BEB-B67EB47D15B6}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109B1D6D-187D-4903-92DA-5B2C7A415830}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>18045.825000000001</v>
+        <v>17857.174999999999</v>
       </c>
       <c r="E4" s="12">
         <v>13145</v>
       </c>
       <c r="F4" s="12">
-        <v>4900.8250000000007</v>
+        <v>4712.1749999999993</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="12">
-        <v>8743.7250000000004</v>
+        <v>7144.2375000000011</v>
       </c>
       <c r="E10" s="12">
         <v>3000</v>
       </c>
       <c r="F10" s="12">
-        <v>5743.7250000000004</v>
+        <v>4144.2375000000011</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133664.45000000001</v>
+        <v>131876.31249999997</v>
       </c>
       <c r="E13" s="14">
         <v>36868</v>
       </c>
       <c r="F13" s="14">
-        <v>96796.45</v>
+        <v>95008.312499999985</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109B1D6D-187D-4903-92DA-5B2C7A415830}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C670157-9D9E-4AE5-BACE-C26D377E31B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="12">
-        <v>7144.2375000000011</v>
+        <v>8744.2125000000015</v>
       </c>
       <c r="E10" s="12">
         <v>3000</v>
       </c>
       <c r="F10" s="12">
-        <v>4144.2375000000011</v>
+        <v>5744.2125000000015</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>131876.31249999997</v>
+        <v>133476.28749999998</v>
       </c>
       <c r="E13" s="14">
         <v>36868</v>
       </c>
       <c r="F13" s="14">
-        <v>95008.312499999985</v>
+        <v>96608.287499999991</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C670157-9D9E-4AE5-BACE-C26D377E31B1}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6BB9CF-CACB-43AA-8DF4-57F0ACD7583A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,10 +671,10 @@
         <v>4026.1374999999998</v>
       </c>
       <c r="E3" s="13">
-        <v>3160</v>
+        <v>3660</v>
       </c>
       <c r="F3" s="13">
-        <v>866.13749999999982</v>
+        <v>366.13749999999982</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>17857.174999999999</v>
+        <v>18452.174999999999</v>
       </c>
       <c r="E4" s="12">
-        <v>13145</v>
+        <v>14125</v>
       </c>
       <c r="F4" s="12">
-        <v>4712.1749999999993</v>
+        <v>4327.1749999999993</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -708,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="12">
-        <v>8038.45</v>
+        <v>7364.1750000000011</v>
       </c>
       <c r="E5" s="13">
-        <v>4170</v>
+        <v>4550</v>
       </c>
       <c r="F5" s="13">
-        <v>3868.45</v>
+        <v>2814.1750000000011</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>33211.424999999981</v>
+        <v>33211.474999999984</v>
       </c>
       <c r="E7" s="13">
-        <v>8436</v>
+        <v>8936</v>
       </c>
       <c r="F7" s="13">
-        <v>24775.424999999981</v>
+        <v>24275.474999999984</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>43380.86250000001</v>
       </c>
       <c r="E9" s="13">
-        <v>4672</v>
+        <v>4832</v>
       </c>
       <c r="F9" s="13">
-        <v>38708.86250000001</v>
+        <v>38548.86250000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="12">
-        <v>8744.2125000000015</v>
+        <v>8821.6125000000011</v>
       </c>
       <c r="E10" s="12">
         <v>3000</v>
       </c>
       <c r="F10" s="12">
-        <v>5744.2125000000015</v>
+        <v>5821.6125000000011</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133476.28749999998</v>
+        <v>133474.46249999999</v>
       </c>
       <c r="E13" s="14">
-        <v>36868</v>
+        <v>39388</v>
       </c>
       <c r="F13" s="14">
-        <v>96608.287499999991</v>
+        <v>94086.462499999994</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6BB9CF-CACB-43AA-8DF4-57F0ACD7583A}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2632BA57-24E6-4D62-8D50-7A340634730A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>33211.474999999984</v>
+        <v>32998.999999999985</v>
       </c>
       <c r="E7" s="13">
         <v>8936</v>
       </c>
       <c r="F7" s="13">
-        <v>24275.474999999984</v>
+        <v>24062.999999999985</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133474.46249999999</v>
+        <v>133261.98749999999</v>
       </c>
       <c r="E13" s="14">
         <v>39388</v>
       </c>
       <c r="F13" s="14">
-        <v>94086.462499999994</v>
+        <v>93873.987499999988</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2632BA57-24E6-4D62-8D50-7A340634730A}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E55173CE-C27C-4A44-B2E2-8A8949B5D3C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="12">
-        <v>7364.1750000000011</v>
+        <v>7364.2250000000004</v>
       </c>
       <c r="E5" s="13">
         <v>4550</v>
       </c>
       <c r="F5" s="13">
-        <v>2814.1750000000011</v>
+        <v>2814.2250000000004</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,10 +751,10 @@
         <v>32998.999999999985</v>
       </c>
       <c r="E7" s="13">
-        <v>8936</v>
+        <v>9656</v>
       </c>
       <c r="F7" s="13">
-        <v>24062.999999999985</v>
+        <v>23342.999999999985</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>43380.86250000001</v>
       </c>
       <c r="E9" s="13">
-        <v>4832</v>
+        <v>5312</v>
       </c>
       <c r="F9" s="13">
-        <v>38548.86250000001</v>
+        <v>38068.86250000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133261.98749999999</v>
+        <v>133262.03749999998</v>
       </c>
       <c r="E13" s="14">
-        <v>39388</v>
+        <v>40588</v>
       </c>
       <c r="F13" s="14">
-        <v>93873.987499999988</v>
+        <v>92674.037499999991</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E55173CE-C27C-4A44-B2E2-8A8949B5D3C4}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E5AB15-56A5-4DAE-91E2-7B97D4A8A934}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,10 +691,10 @@
         <v>18452.174999999999</v>
       </c>
       <c r="E4" s="12">
-        <v>14125</v>
+        <v>16375</v>
       </c>
       <c r="F4" s="12">
-        <v>4327.1749999999993</v>
+        <v>2077.1749999999993</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -708,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="12">
-        <v>7364.2250000000004</v>
+        <v>7394.25</v>
       </c>
       <c r="E5" s="13">
-        <v>4550</v>
+        <v>6800</v>
       </c>
       <c r="F5" s="13">
-        <v>2814.2250000000004</v>
+        <v>594.25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>9078.2124999999978</v>
+        <v>10628.212499999998</v>
       </c>
       <c r="E6" s="12">
         <v>285</v>
       </c>
       <c r="F6" s="12">
-        <v>8793.2124999999978</v>
+        <v>10343.212499999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>32998.999999999985</v>
+        <v>31124.274999999987</v>
       </c>
       <c r="E7" s="13">
-        <v>9656</v>
+        <v>15581</v>
       </c>
       <c r="F7" s="13">
-        <v>23342.999999999985</v>
+        <v>15543.274999999987</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,13 +768,13 @@
         <v>18</v>
       </c>
       <c r="D8" s="12">
-        <v>5353.0874999999996</v>
+        <v>3180.4875000000002</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="12">
-        <v>5353.0874999999996</v>
+        <v>3180.4875000000002</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>43380.86250000001</v>
+        <v>42241.650000000016</v>
       </c>
       <c r="E9" s="13">
-        <v>5312</v>
+        <v>5507</v>
       </c>
       <c r="F9" s="13">
-        <v>38068.86250000001</v>
+        <v>36734.650000000016</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>133262.03749999998</v>
+        <v>129655.52499999999</v>
       </c>
       <c r="E13" s="14">
-        <v>40588</v>
+        <v>51208</v>
       </c>
       <c r="F13" s="14">
-        <v>92674.037499999991</v>
+        <v>78447.524999999994</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E5AB15-56A5-4DAE-91E2-7B97D4A8A934}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4591725-D95B-4EC2-BD68-BD61BDB8217A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,10 +671,10 @@
         <v>4026.1374999999998</v>
       </c>
       <c r="E3" s="13">
-        <v>3660</v>
+        <v>3960</v>
       </c>
       <c r="F3" s="13">
-        <v>366.13749999999982</v>
+        <v>66.137499999999818</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>10628.212499999998</v>
+        <v>11333.075000000001</v>
       </c>
       <c r="E6" s="12">
-        <v>285</v>
+        <v>4335</v>
       </c>
       <c r="F6" s="12">
-        <v>10343.212499999998</v>
+        <v>6998.0750000000007</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>31124.274999999987</v>
+        <v>33223.649999999987</v>
       </c>
       <c r="E7" s="13">
-        <v>15581</v>
+        <v>15861</v>
       </c>
       <c r="F7" s="13">
-        <v>15543.274999999987</v>
+        <v>17362.649999999987</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -771,10 +771,10 @@
         <v>3180.4875000000002</v>
       </c>
       <c r="E8" s="12">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="F8" s="12">
-        <v>3180.4875000000002</v>
+        <v>1960.4875000000002</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -811,10 +811,10 @@
         <v>8821.6125000000011</v>
       </c>
       <c r="E10" s="12">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="F10" s="12">
-        <v>5821.6125000000011</v>
+        <v>5421.6125000000011</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>129655.52499999999</v>
+        <v>132459.76249999998</v>
       </c>
       <c r="E13" s="14">
-        <v>51208</v>
+        <v>57458</v>
       </c>
       <c r="F13" s="14">
-        <v>78447.524999999994</v>
+        <v>75001.762499999997</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4591725-D95B-4EC2-BD68-BD61BDB8217A}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CA930F8-4C2F-42C8-B661-BE8C7ADB9709}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,10 +711,10 @@
         <v>7394.25</v>
       </c>
       <c r="E5" s="13">
-        <v>6800</v>
+        <v>6890</v>
       </c>
       <c r="F5" s="13">
-        <v>594.25</v>
+        <v>504.25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>11333.075000000001</v>
+        <v>9806.2374999999993</v>
       </c>
       <c r="E6" s="12">
         <v>4335</v>
       </c>
       <c r="F6" s="12">
-        <v>6998.0750000000007</v>
+        <v>5471.2374999999993</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>42241.650000000016</v>
       </c>
       <c r="E9" s="13">
-        <v>5507</v>
+        <v>6227</v>
       </c>
       <c r="F9" s="13">
-        <v>36734.650000000016</v>
+        <v>36014.650000000016</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -851,10 +851,10 @@
         <v>1914.65</v>
       </c>
       <c r="E12" s="12">
-        <v>0</v>
+        <v>1836.875</v>
       </c>
       <c r="F12" s="12">
-        <v>1914.65</v>
+        <v>77.775000000000091</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>132459.76249999998</v>
+        <v>130932.92499999999</v>
       </c>
       <c r="E13" s="14">
-        <v>57458</v>
+        <v>60104.875</v>
       </c>
       <c r="F13" s="14">
-        <v>75001.762499999997</v>
+        <v>70828.049999999988</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CA930F8-4C2F-42C8-B661-BE8C7ADB9709}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BCF6406-EB14-43FA-B1AD-B464595E9D8B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BCF6406-EB14-43FA-B1AD-B464595E9D8B}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6BF27A9-9795-4E2A-AA7F-F9D75AE70678}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>9806.2374999999993</v>
+        <v>9806.2875000000004</v>
       </c>
       <c r="E6" s="12">
         <v>4335</v>
       </c>
       <c r="F6" s="12">
-        <v>5471.2374999999993</v>
+        <v>5471.2875000000004</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="12">
-        <v>33223.649999999987</v>
+        <v>33223.774999999987</v>
       </c>
       <c r="E7" s="13">
         <v>15861</v>
       </c>
       <c r="F7" s="13">
-        <v>17362.649999999987</v>
+        <v>17362.774999999987</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>42241.650000000016</v>
+        <v>41209.750000000007</v>
       </c>
       <c r="E9" s="13">
         <v>6227</v>
       </c>
       <c r="F9" s="13">
-        <v>36014.650000000016</v>
+        <v>34982.750000000007</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>130932.92499999999</v>
+        <v>129901.19999999998</v>
       </c>
       <c r="E13" s="14">
         <v>60104.875</v>
       </c>
       <c r="F13" s="14">
-        <v>70828.049999999988</v>
+        <v>69796.324999999983</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6BF27A9-9795-4E2A-AA7F-F9D75AE70678}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693E5934-A769-4A61-B3DF-D564321F83A9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,10 +691,10 @@
         <v>18452.174999999999</v>
       </c>
       <c r="E4" s="12">
-        <v>16375</v>
+        <v>17115</v>
       </c>
       <c r="F4" s="12">
-        <v>2077.1749999999993</v>
+        <v>1337.1749999999993</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>9806.2875000000004</v>
+        <v>9828.3375000000015</v>
       </c>
       <c r="E6" s="12">
         <v>4335</v>
       </c>
       <c r="F6" s="12">
-        <v>5471.2875000000004</v>
+        <v>5493.3375000000015</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,10 +751,10 @@
         <v>33223.774999999987</v>
       </c>
       <c r="E7" s="13">
-        <v>15861</v>
+        <v>16601</v>
       </c>
       <c r="F7" s="13">
-        <v>17362.774999999987</v>
+        <v>16622.774999999987</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>41209.750000000007</v>
+        <v>41817.25</v>
       </c>
       <c r="E9" s="13">
-        <v>6227</v>
+        <v>6167</v>
       </c>
       <c r="F9" s="13">
-        <v>34982.750000000007</v>
+        <v>35650.25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>129901.19999999998</v>
+        <v>130530.74999999999</v>
       </c>
       <c r="E13" s="14">
-        <v>60104.875</v>
+        <v>61524.875</v>
       </c>
       <c r="F13" s="14">
-        <v>69796.324999999983</v>
+        <v>69005.874999999985</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693E5934-A769-4A61-B3DF-D564321F83A9}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE64D034-C32F-42E3-8612-76715662F2FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -711,10 +711,10 @@
         <v>7394.25</v>
       </c>
       <c r="E5" s="13">
-        <v>6890</v>
+        <v>6900</v>
       </c>
       <c r="F5" s="13">
-        <v>504.25</v>
+        <v>494.25</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>41817.25</v>
       </c>
       <c r="E9" s="13">
-        <v>6167</v>
+        <v>6227</v>
       </c>
       <c r="F9" s="13">
-        <v>35650.25</v>
+        <v>35590.25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -867,10 +867,10 @@
         <v>130530.74999999999</v>
       </c>
       <c r="E13" s="14">
-        <v>61524.875</v>
+        <v>61594.875</v>
       </c>
       <c r="F13" s="14">
-        <v>69005.874999999985</v>
+        <v>68935.874999999985</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE64D034-C32F-42E3-8612-76715662F2FE}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8303F7B3-6ECC-4169-BE81-636FCB73ECCD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>18452.174999999999</v>
+        <v>15657.800000000003</v>
       </c>
       <c r="E4" s="12">
         <v>17115</v>
       </c>
       <c r="F4" s="12">
-        <v>1337.1749999999993</v>
+        <v>-1457.1999999999971</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>41817.25</v>
+        <v>42317.25</v>
       </c>
       <c r="E9" s="13">
         <v>6227</v>
       </c>
       <c r="F9" s="13">
-        <v>35590.25</v>
+        <v>36090.25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -831,10 +831,10 @@
         <v>1872.075</v>
       </c>
       <c r="E11" s="13">
-        <v>0</v>
+        <v>1590</v>
       </c>
       <c r="F11" s="13">
-        <v>1872.075</v>
+        <v>282.07500000000005</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -851,10 +851,10 @@
         <v>1914.65</v>
       </c>
       <c r="E12" s="12">
-        <v>1836.875</v>
+        <v>1916.875</v>
       </c>
       <c r="F12" s="12">
-        <v>77.775000000000091</v>
+        <v>-2.2249999999999091</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>130530.74999999999</v>
+        <v>128236.37499999999</v>
       </c>
       <c r="E13" s="14">
-        <v>61594.875</v>
+        <v>63264.875</v>
       </c>
       <c r="F13" s="14">
-        <v>68935.874999999985</v>
+        <v>64971.499999999993</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8303F7B3-6ECC-4169-BE81-636FCB73ECCD}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{200412E3-F097-40E5-8387-403ABD16B284}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,10 +671,10 @@
         <v>4026.1374999999998</v>
       </c>
       <c r="E3" s="13">
-        <v>3960</v>
+        <v>3961</v>
       </c>
       <c r="F3" s="13">
-        <v>66.137499999999818</v>
+        <v>65.137499999999818</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="12">
-        <v>15657.800000000003</v>
+        <v>17858.550000000003</v>
       </c>
       <c r="E4" s="12">
         <v>17115</v>
       </c>
       <c r="F4" s="12">
-        <v>-1457.1999999999971</v>
+        <v>743.55000000000291</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="12">
-        <v>9828.3375000000015</v>
+        <v>9197.2125000000015</v>
       </c>
       <c r="E6" s="12">
-        <v>4335</v>
+        <v>5835</v>
       </c>
       <c r="F6" s="12">
-        <v>5493.3375000000015</v>
+        <v>3362.2125000000015</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,10 +751,10 @@
         <v>33223.774999999987</v>
       </c>
       <c r="E7" s="13">
-        <v>16601</v>
+        <v>18101</v>
       </c>
       <c r="F7" s="13">
-        <v>16622.774999999987</v>
+        <v>15122.774999999987</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="12">
-        <v>42317.25</v>
+        <v>42443.149999999994</v>
       </c>
       <c r="E9" s="13">
-        <v>6227</v>
+        <v>6390</v>
       </c>
       <c r="F9" s="13">
-        <v>36090.25</v>
+        <v>36053.149999999994</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="14">
-        <v>128236.37499999999</v>
+        <v>129931.89999999998</v>
       </c>
       <c r="E13" s="14">
-        <v>63264.875</v>
+        <v>66428.875</v>
       </c>
       <c r="F13" s="14">
-        <v>64971.499999999993</v>
+        <v>63503.024999999987</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{200412E3-F097-40E5-8387-403ABD16B284}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1434BF2-02D2-4BB8-B75A-73DA187D91A3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>OFERTA TOTAL (Bls)</t>
   </si>
@@ -48,9 +52,6 @@
   </si>
   <si>
     <t>Semilllero</t>
-  </si>
-  <si>
-    <t>Varied</t>
   </si>
   <si>
     <t>Variedad</t>
@@ -129,7 +130,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
@@ -142,30 +144,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -177,26 +183,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EA72E"/>
-        <bgColor rgb="FF4EA72E"/>
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAF2D0"/>
-        <bgColor rgb="FFDAF2D0"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E6A2"/>
-        <bgColor rgb="FFB5E6A2"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor theme="9" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EA72E"/>
-        <bgColor rgb="FFDAF2D0"/>
+        <fgColor theme="9"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,80 +212,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="dashed">
-        <color indexed="64"/>
-      </top>
-      <bottom style="dashed">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -293,50 +225,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -350,6 +357,102 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Calidad CAMPO"/>
+      <sheetName val="Compromiso"/>
+      <sheetName val="Hoja1"/>
+      <sheetName val="Cartas Calidad"/>
+      <sheetName val="Info Orden de Carga"/>
+      <sheetName val="Orden de Carga"/>
+      <sheetName val="MASTER"/>
+      <sheetName val="Ubicacion "/>
+      <sheetName val="Detalle Silobolsa"/>
+      <sheetName val="Resumen por Firma"/>
+      <sheetName val="_Calc"/>
+      <sheetName val="Resumen Campaña"/>
+      <sheetName val="Escenarios"/>
+      <sheetName val="_Datos"/>
+      <sheetName val="Panel Interactivo"/>
+      <sheetName val="Hoja3"/>
+      <sheetName val="Hoja2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Balanza"/>
+      <sheetName val="Orden int."/>
+      <sheetName val="Intermedio"/>
+      <sheetName val="Prod. Final"/>
+      <sheetName val="Intermedio curado"/>
+      <sheetName val="Plan Curado"/>
+      <sheetName val="Chequeo"/>
+      <sheetName val="Ventas Finn"/>
+      <sheetName val="Despacho"/>
+      <sheetName val="Orden de carga"/>
+      <sheetName val="MASTER"/>
+      <sheetName val="Calendario Produccion"/>
+      <sheetName val="Cartel Bolsa M"/>
+      <sheetName val="Rotulos"/>
+      <sheetName val="Stock 2026"/>
+      <sheetName val="RepStage"/>
+      <sheetName val="_ListasLotes"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -624,253 +727,283 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C3,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C3)/40)</f>
+        <v>4026.1374999999998</v>
+      </c>
+      <c r="E3" s="8">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C3)/40</f>
+        <v>3961</v>
+      </c>
+      <c r="F3" s="8">
+        <f>+D3-E3</f>
+        <v>65.137499999999818</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C4,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C4)/40)</f>
+        <v>17838.550000000003</v>
+      </c>
+      <c r="E4" s="7">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C4)/40</f>
+        <v>17115</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F10" si="0">+D4-E4</f>
+        <v>723.55000000000291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="12">
-        <v>4026.1374999999998</v>
-      </c>
-      <c r="E3" s="13">
-        <v>3961</v>
-      </c>
-      <c r="F3" s="13">
-        <v>65.137499999999818</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="12">
-        <v>17858.550000000003</v>
-      </c>
-      <c r="E4" s="12">
-        <v>17115</v>
-      </c>
-      <c r="F4" s="12">
-        <v>743.55000000000291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C5,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C5)/40)</f>
+        <v>7394.25</v>
+      </c>
+      <c r="E5" s="8">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C5)/40</f>
+        <v>6900</v>
+      </c>
+      <c r="F5" s="8">
+        <f>+D5-E5</f>
+        <v>494.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="12">
-        <v>7394.25</v>
-      </c>
-      <c r="E5" s="13">
-        <v>6900</v>
-      </c>
-      <c r="F5" s="13">
-        <v>494.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C6,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C6)/40)</f>
+        <v>9197.2125000000015</v>
+      </c>
+      <c r="E6" s="7">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C6)/40</f>
+        <v>5835</v>
+      </c>
+      <c r="F6" s="7">
+        <f>+D6-E6</f>
+        <v>3362.2125000000015</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="12">
-        <v>9197.2125000000015</v>
-      </c>
-      <c r="E6" s="12">
-        <v>5835</v>
-      </c>
-      <c r="F6" s="12">
-        <v>3362.2125000000015</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C7,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C7)/40)</f>
+        <v>28485.024999999998</v>
+      </c>
+      <c r="E7" s="8">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C7)/40</f>
+        <v>18101</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="0"/>
+        <v>10384.024999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="12">
-        <v>33223.774999999987</v>
-      </c>
-      <c r="E7" s="13">
-        <v>18101</v>
-      </c>
-      <c r="F7" s="13">
-        <v>15122.774999999987</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C8,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C8)/40)</f>
+        <v>3180.4875000000002</v>
+      </c>
+      <c r="E8" s="7">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C8)/40</f>
+        <v>1220</v>
+      </c>
+      <c r="F8" s="7">
+        <f>+D8-E8</f>
+        <v>1960.4875000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="12">
-        <v>3180.4875000000002</v>
-      </c>
-      <c r="E8" s="12">
-        <v>1220</v>
-      </c>
-      <c r="F8" s="12">
-        <v>1960.4875000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C9,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C9)/40)</f>
+        <v>42443.149999999994</v>
+      </c>
+      <c r="E9" s="8">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C9)/40</f>
+        <v>6390</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="0"/>
+        <v>36053.149999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="12">
-        <v>42443.149999999994</v>
-      </c>
-      <c r="E9" s="13">
-        <v>6390</v>
-      </c>
-      <c r="F9" s="13">
-        <v>36053.149999999994</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C10,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C10)/40)</f>
+        <v>8821.6125000000011</v>
+      </c>
+      <c r="E10" s="7">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C10)/40</f>
+        <v>3400</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>5421.6125000000011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="12">
-        <v>8821.6125000000011</v>
-      </c>
-      <c r="E10" s="12">
-        <v>3400</v>
-      </c>
-      <c r="F10" s="12">
-        <v>5421.6125000000011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C11,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C11)/40)</f>
+        <v>1872.075</v>
+      </c>
+      <c r="E11" s="8">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C11)/40</f>
+        <v>1590</v>
+      </c>
+      <c r="F11" s="8">
+        <f>+D11-E11</f>
+        <v>282.07500000000005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="12">
-        <v>1872.075</v>
-      </c>
-      <c r="E11" s="13">
-        <v>1590</v>
-      </c>
-      <c r="F11" s="13">
-        <v>282.07500000000005</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="7">
+        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C12,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C12)/40)</f>
+        <v>1914.65</v>
+      </c>
+      <c r="E12" s="7">
+        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C12)/40</f>
+        <v>1896.875</v>
+      </c>
+      <c r="F12" s="7">
+        <f>+D12-E12</f>
+        <v>17.775000000000091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="12">
-        <v>1914.65</v>
-      </c>
-      <c r="E12" s="12">
-        <v>1916.875</v>
-      </c>
-      <c r="F12" s="12">
-        <v>-2.2249999999999091</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="14">
-        <v>129931.89999999998</v>
-      </c>
-      <c r="E13" s="14">
-        <v>66428.875</v>
-      </c>
-      <c r="F13" s="14">
-        <v>63503.024999999987</v>
+      <c r="D13" s="13">
+        <f>+SUM(D3:D12)</f>
+        <v>125173.15</v>
+      </c>
+      <c r="E13" s="13">
+        <f>+SUM(E3:E12)</f>
+        <v>66408.875</v>
+      </c>
+      <c r="F13" s="13">
+        <f>+SUM(F3:F12)</f>
+        <v>58764.275000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,17 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1434BF2-02D2-4BB8-B75A-73DA187D91A3}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6356E7AF-D1ED-4D39-B9C8-0B9B660FE97E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -357,102 +353,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Calidad CAMPO"/>
-      <sheetName val="Compromiso"/>
-      <sheetName val="Hoja1"/>
-      <sheetName val="Cartas Calidad"/>
-      <sheetName val="Info Orden de Carga"/>
-      <sheetName val="Orden de Carga"/>
-      <sheetName val="MASTER"/>
-      <sheetName val="Ubicacion "/>
-      <sheetName val="Detalle Silobolsa"/>
-      <sheetName val="Resumen por Firma"/>
-      <sheetName val="_Calc"/>
-      <sheetName val="Resumen Campaña"/>
-      <sheetName val="Escenarios"/>
-      <sheetName val="_Datos"/>
-      <sheetName val="Panel Interactivo"/>
-      <sheetName val="Hoja3"/>
-      <sheetName val="Hoja2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Balanza"/>
-      <sheetName val="Orden int."/>
-      <sheetName val="Intermedio"/>
-      <sheetName val="Prod. Final"/>
-      <sheetName val="Intermedio curado"/>
-      <sheetName val="Plan Curado"/>
-      <sheetName val="Chequeo"/>
-      <sheetName val="Ventas Finn"/>
-      <sheetName val="Despacho"/>
-      <sheetName val="Orden de carga"/>
-      <sheetName val="MASTER"/>
-      <sheetName val="Calendario Produccion"/>
-      <sheetName val="Cartel Bolsa M"/>
-      <sheetName val="Rotulos"/>
-      <sheetName val="Stock 2026"/>
-      <sheetName val="RepStage"/>
-      <sheetName val="_ListasLotes"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,15 +668,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C3,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C3)/40)</f>
         <v>4026.1374999999998</v>
       </c>
       <c r="E3" s="8">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C3)/40</f>
         <v>3961</v>
       </c>
       <c r="F3" s="8">
-        <f>+D3-E3</f>
         <v>65.137499999999818</v>
       </c>
     </row>
@@ -791,16 +688,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C4,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C4)/40)</f>
-        <v>17838.550000000003</v>
+        <v>19641.775000000001</v>
       </c>
       <c r="E4" s="7">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C4)/40</f>
         <v>17115</v>
       </c>
       <c r="F4" s="7">
-        <f t="shared" ref="F4:F10" si="0">+D4-E4</f>
-        <v>723.55000000000291</v>
+        <v>2526.7750000000015</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -814,15 +708,12 @@
         <v>11</v>
       </c>
       <c r="D5" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C5,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C5)/40)</f>
         <v>7394.25</v>
       </c>
       <c r="E5" s="8">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C5)/40</f>
         <v>6900</v>
       </c>
       <c r="F5" s="8">
-        <f>+D5-E5</f>
         <v>494.25</v>
       </c>
     </row>
@@ -837,15 +728,12 @@
         <v>13</v>
       </c>
       <c r="D6" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C6,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C6)/40)</f>
         <v>9197.2125000000015</v>
       </c>
       <c r="E6" s="7">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C6)/40</f>
         <v>5835</v>
       </c>
       <c r="F6" s="7">
-        <f>+D6-E6</f>
         <v>3362.2125000000015</v>
       </c>
     </row>
@@ -860,16 +748,13 @@
         <v>15</v>
       </c>
       <c r="D7" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C7,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C7)/40)</f>
-        <v>28485.024999999998</v>
+        <v>29285.024999999998</v>
       </c>
       <c r="E7" s="8">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C7)/40</f>
         <v>18101</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" si="0"/>
-        <v>10384.024999999998</v>
+        <v>11184.024999999998</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -883,15 +768,12 @@
         <v>17</v>
       </c>
       <c r="D8" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C8,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C8)/40)</f>
         <v>3180.4875000000002</v>
       </c>
       <c r="E8" s="7">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C8)/40</f>
         <v>1220</v>
       </c>
       <c r="F8" s="7">
-        <f>+D8-E8</f>
         <v>1960.4875000000002</v>
       </c>
     </row>
@@ -906,15 +788,12 @@
         <v>19</v>
       </c>
       <c r="D9" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C9,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C9)/40)</f>
         <v>42443.149999999994</v>
       </c>
       <c r="E9" s="8">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C9)/40</f>
         <v>6390</v>
       </c>
       <c r="F9" s="8">
-        <f t="shared" si="0"/>
         <v>36053.149999999994</v>
       </c>
     </row>
@@ -929,15 +808,12 @@
         <v>21</v>
       </c>
       <c r="D10" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C10,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C10)/40)</f>
         <v>8821.6125000000011</v>
       </c>
       <c r="E10" s="7">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C10)/40</f>
         <v>3400</v>
       </c>
       <c r="F10" s="7">
-        <f t="shared" si="0"/>
         <v>5421.6125000000011</v>
       </c>
     </row>
@@ -952,15 +828,12 @@
         <v>24</v>
       </c>
       <c r="D11" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C11,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C11)/40)</f>
         <v>1872.075</v>
       </c>
       <c r="E11" s="8">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C11)/40</f>
         <v>1590</v>
       </c>
       <c r="F11" s="8">
-        <f>+D11-E11</f>
         <v>282.07500000000005</v>
       </c>
     </row>
@@ -975,15 +848,12 @@
         <v>26</v>
       </c>
       <c r="D12" s="7">
-        <f>+SUMIFS([1]!Tablacalidad[Tns],[1]!Tablacalidad[Variedades],$C12,[1]!Tablacalidad[Calidad],"SI",[1]!Tablacalidad[Estado],"disp")*1000*0.85/40+(SUMIFS([2]!Intermedio[Kg x Partida],[2]!Intermedio[Variedad],C12)/40)</f>
         <v>1914.65</v>
       </c>
       <c r="E12" s="7">
-        <f>+SUMIFS([2]!Ventas[Kg Total],[2]!Ventas[Variedad],$C12)/40</f>
         <v>1896.875</v>
       </c>
       <c r="F12" s="7">
-        <f>+D12-E12</f>
         <v>17.775000000000091</v>
       </c>
     </row>
@@ -994,16 +864,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="13">
-        <f>+SUM(D3:D12)</f>
-        <v>125173.15</v>
+        <v>127776.37499999999</v>
       </c>
       <c r="E13" s="13">
-        <f>+SUM(E3:E12)</f>
         <v>66408.875</v>
       </c>
       <c r="F13" s="13">
-        <f>+SUM(F3:F12)</f>
-        <v>58764.275000000001</v>
+        <v>61367.499999999993</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6356E7AF-D1ED-4D39-B9C8-0B9B660FE97E}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D190DE-B14D-46BD-B505-13337C465C90}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D190DE-B14D-46BD-B505-13337C465C90}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5919D8A7-490D-4A4C-A23F-B1A5D059FB82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -748,13 +748,13 @@
         <v>15</v>
       </c>
       <c r="D7" s="7">
-        <v>29285.024999999998</v>
+        <v>30930.625</v>
       </c>
       <c r="E7" s="8">
         <v>18101</v>
       </c>
       <c r="F7" s="8">
-        <v>11184.024999999998</v>
+        <v>12829.625</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="13">
-        <v>127776.37499999999</v>
+        <v>129421.97499999999</v>
       </c>
       <c r="E13" s="13">
         <v>66408.875</v>
       </c>
       <c r="F13" s="13">
-        <v>61367.499999999993</v>
+        <v>63013.1</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5919D8A7-490D-4A4C-A23F-B1A5D059FB82}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F9C6BF2-7E5D-4BA2-B5B5-B5998EF99258}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -688,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="7">
-        <v>19641.775000000001</v>
+        <v>20622.775000000001</v>
       </c>
       <c r="E4" s="7">
-        <v>17115</v>
+        <v>17260</v>
       </c>
       <c r="F4" s="7">
-        <v>2526.7750000000015</v>
+        <v>3362.7750000000015</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -731,10 +731,10 @@
         <v>9197.2125000000015</v>
       </c>
       <c r="E6" s="7">
-        <v>5835</v>
+        <v>6075</v>
       </c>
       <c r="F6" s="7">
-        <v>3362.2125000000015</v>
+        <v>3122.2125000000015</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>15</v>
       </c>
       <c r="D7" s="7">
-        <v>30930.625</v>
+        <v>33580.625</v>
       </c>
       <c r="E7" s="8">
-        <v>18101</v>
+        <v>18301</v>
       </c>
       <c r="F7" s="8">
-        <v>12829.625</v>
+        <v>15279.625</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>42443.149999999994</v>
       </c>
       <c r="E9" s="8">
-        <v>6390</v>
+        <v>6870</v>
       </c>
       <c r="F9" s="8">
-        <v>36053.149999999994</v>
+        <v>35573.149999999994</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="13">
-        <v>129421.97499999999</v>
+        <v>133052.97500000001</v>
       </c>
       <c r="E13" s="13">
-        <v>66408.875</v>
+        <v>67473.875</v>
       </c>
       <c r="F13" s="13">
-        <v>63013.1</v>
+        <v>65579.099999999991</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F9C6BF2-7E5D-4BA2-B5B5-B5998EF99258}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A053780-0992-4A1B-A5D8-970F0E2E30F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,10 +691,10 @@
         <v>20622.775000000001</v>
       </c>
       <c r="E4" s="7">
-        <v>17260</v>
+        <v>18280</v>
       </c>
       <c r="F4" s="7">
-        <v>3362.7750000000015</v>
+        <v>2342.7750000000015</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -751,10 +751,10 @@
         <v>33580.625</v>
       </c>
       <c r="E7" s="8">
-        <v>18301</v>
+        <v>15537</v>
       </c>
       <c r="F7" s="8">
-        <v>15279.625</v>
+        <v>18043.625</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,10 +791,10 @@
         <v>42443.149999999994</v>
       </c>
       <c r="E9" s="8">
-        <v>6870</v>
+        <v>7155</v>
       </c>
       <c r="F9" s="8">
-        <v>35573.149999999994</v>
+        <v>35288.149999999994</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -811,10 +811,10 @@
         <v>8821.6125000000011</v>
       </c>
       <c r="E10" s="7">
-        <v>3400</v>
+        <v>3540</v>
       </c>
       <c r="F10" s="7">
-        <v>5421.6125000000011</v>
+        <v>5281.6125000000011</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -867,10 +867,10 @@
         <v>133052.97500000001</v>
       </c>
       <c r="E13" s="13">
-        <v>67473.875</v>
+        <v>66154.875</v>
       </c>
       <c r="F13" s="13">
-        <v>65579.099999999991</v>
+        <v>66898.099999999991</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A053780-0992-4A1B-A5D8-970F0E2E30F9}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E6F83F6-B8BC-4BA6-A93D-DF77559C169E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -668,13 +668,13 @@
         <v>8</v>
       </c>
       <c r="D3" s="7">
-        <v>4026.1374999999998</v>
+        <v>1573</v>
       </c>
       <c r="E3" s="8">
         <v>3961</v>
       </c>
       <c r="F3" s="8">
-        <v>65.137499999999818</v>
+        <v>-2388</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="7">
-        <v>20622.775000000001</v>
+        <v>19968</v>
       </c>
       <c r="E4" s="7">
         <v>18280</v>
       </c>
       <c r="F4" s="7">
-        <v>2342.7750000000015</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -708,13 +708,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="7">
-        <v>7394.25</v>
+        <v>7394</v>
       </c>
       <c r="E5" s="8">
         <v>6900</v>
       </c>
       <c r="F5" s="8">
-        <v>494.25</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="7">
-        <v>9197.2125000000015</v>
+        <v>9197</v>
       </c>
       <c r="E6" s="7">
         <v>6075</v>
       </c>
       <c r="F6" s="7">
-        <v>3122.2125000000015</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>15</v>
       </c>
       <c r="D7" s="7">
-        <v>33580.625</v>
+        <v>33581</v>
       </c>
       <c r="E7" s="8">
         <v>15537</v>
       </c>
       <c r="F7" s="8">
-        <v>18043.625</v>
+        <v>18044</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,13 +768,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="7">
-        <v>3180.4875000000002</v>
+        <v>3180</v>
       </c>
       <c r="E8" s="7">
         <v>1220</v>
       </c>
       <c r="F8" s="7">
-        <v>1960.4875000000002</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>19</v>
       </c>
       <c r="D9" s="7">
-        <v>42443.149999999994</v>
+        <v>42443</v>
       </c>
       <c r="E9" s="8">
         <v>7155</v>
       </c>
       <c r="F9" s="8">
-        <v>35288.149999999994</v>
+        <v>35288</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="D10" s="7">
-        <v>8821.6125000000011</v>
+        <v>8822</v>
       </c>
       <c r="E10" s="7">
         <v>3540</v>
       </c>
       <c r="F10" s="7">
-        <v>5281.6125000000011</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -828,13 +828,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="7">
-        <v>1872.075</v>
+        <v>1872</v>
       </c>
       <c r="E11" s="8">
         <v>1590</v>
       </c>
       <c r="F11" s="8">
-        <v>282.07500000000005</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -848,13 +848,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="7">
-        <v>1914.65</v>
+        <v>1915</v>
       </c>
       <c r="E12" s="7">
-        <v>1896.875</v>
+        <v>1897</v>
       </c>
       <c r="F12" s="7">
-        <v>17.775000000000091</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="13">
-        <v>133052.97500000001</v>
+        <v>129945</v>
       </c>
       <c r="E13" s="13">
-        <v>66154.875</v>
+        <v>66155</v>
       </c>
       <c r="F13" s="13">
-        <v>66898.099999999991</v>
+        <v>63790</v>
       </c>
     </row>
   </sheetData>

--- a/ventas.xlsx
+++ b/ventas.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dshnossrl-my.sharepoint.com/personal/dario_besler_dshnossrl_onmicrosoft_com/Documents/Escritorio/Proyecto consultas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E6F83F6-B8BC-4BA6-A93D-DF77559C169E}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_F25DC773A252ABDACC10488251DE5BF45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98FE8DDD-EBF1-4B73-9CE7-E0BCF0D9D5D5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oferta - Vane" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -668,13 +668,13 @@
         <v>8</v>
       </c>
       <c r="D3" s="7">
-        <v>1573</v>
+        <v>3972.8249999999998</v>
       </c>
       <c r="E3" s="8">
         <v>3961</v>
       </c>
       <c r="F3" s="8">
-        <v>-2388</v>
+        <v>11.824999999999818</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="7">
-        <v>19968</v>
+        <v>22778.275000000001</v>
       </c>
       <c r="E4" s="7">
-        <v>18280</v>
+        <v>20025</v>
       </c>
       <c r="F4" s="7">
-        <v>1688</v>
+        <v>2753.2750000000015</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -708,13 +708,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="7">
-        <v>7394</v>
+        <v>7394.25</v>
       </c>
       <c r="E5" s="8">
-        <v>6900</v>
+        <v>7494</v>
       </c>
       <c r="F5" s="8">
-        <v>494</v>
+        <v>-99.75</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -728,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="7">
-        <v>9197</v>
+        <v>9197.2125000000015</v>
       </c>
       <c r="E6" s="7">
         <v>6075</v>
       </c>
       <c r="F6" s="7">
-        <v>3122</v>
+        <v>3122.2125000000015</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -748,13 +748,13 @@
         <v>15</v>
       </c>
       <c r="D7" s="7">
-        <v>33581</v>
+        <v>33561.375</v>
       </c>
       <c r="E7" s="8">
-        <v>15537</v>
+        <v>16051</v>
       </c>
       <c r="F7" s="8">
-        <v>18044</v>
+        <v>17501.375</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -768,13 +768,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="7">
-        <v>3180</v>
+        <v>3180.4875000000002</v>
       </c>
       <c r="E8" s="7">
         <v>1220</v>
       </c>
       <c r="F8" s="7">
-        <v>1960</v>
+        <v>1960.4875000000002</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,13 +788,13 @@
         <v>19</v>
       </c>
       <c r="D9" s="7">
-        <v>42443</v>
+        <v>41577.999999999993</v>
       </c>
       <c r="E9" s="8">
-        <v>7155</v>
+        <v>7175</v>
       </c>
       <c r="F9" s="8">
-        <v>35288</v>
+        <v>34402.999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="D10" s="7">
-        <v>8822</v>
+        <v>8821.6125000000011</v>
       </c>
       <c r="E10" s="7">
         <v>3540</v>
       </c>
       <c r="F10" s="7">
-        <v>5282</v>
+        <v>5281.6125000000011</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -828,13 +828,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="7">
-        <v>1872</v>
+        <v>1872.075</v>
       </c>
       <c r="E11" s="8">
         <v>1590</v>
       </c>
       <c r="F11" s="8">
-        <v>282</v>
+        <v>282.07500000000005</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -848,13 +848,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="7">
-        <v>1915</v>
+        <v>1914.65</v>
       </c>
       <c r="E12" s="7">
-        <v>1897</v>
+        <v>1896.875</v>
       </c>
       <c r="F12" s="7">
-        <v>18</v>
+        <v>17.775000000000091</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -864,13 +864,13 @@
         <v>27</v>
       </c>
       <c r="D13" s="13">
-        <v>129945</v>
+        <v>134270.76249999998</v>
       </c>
       <c r="E13" s="13">
-        <v>66155</v>
+        <v>69027.875</v>
       </c>
       <c r="F13" s="13">
-        <v>63790</v>
+        <v>65233.887499999997</v>
       </c>
     </row>
   </sheetData>
